--- a/public/post/drafts/weekly-picks/2025Lillehammer/men-points.xlsx
+++ b/public/post/drafts/weekly-picks/2025Lillehammer/men-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="403">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
-    <t xml:space="preserve">71.0838731005212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5185098396493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8349876600545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181.437370600225</t>
+    <t xml:space="preserve">75.0980180212452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5185098399798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9968367318724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.613364593097</t>
   </si>
   <si>
     <t xml:space="preserve">Johannes Høsflot Klæbo</t>
@@ -65,85 +65,127 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4941887842013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.1014446041303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.595633388332</t>
+    <t xml:space="preserve">92.4941887838799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5854189297204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.0796077136</t>
   </si>
   <si>
     <t xml:space="preserve">Simen Hegstad Krüger</t>
   </si>
   <si>
-    <t xml:space="preserve">81.5595937577665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8750033099189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.434597067685</t>
+    <t xml:space="preserve">69.3629562632598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.5064605764919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.869416839752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gus Schumacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0701133037478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5493052534631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5563495488423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.175768106053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federico Pellegrino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5356658152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.6206128796184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5294984954749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.685777190297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Vermeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5219020524708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6515888070634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.781937668404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.955428527938</t>
   </si>
   <si>
     <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
   </si>
   <si>
-    <t xml:space="preserve">76.6169491031143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.4729792623157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.08992836543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federico Pellegrino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0858499819185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.6206128793473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5240054773368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.230468338603</t>
+    <t xml:space="preserve">68.8033243876634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.00606153374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.809385921403</t>
   </si>
   <si>
     <t xml:space="preserve">Pål Golberg</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6579397401989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0694211033983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.727360843597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Vermeulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9446284316745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6515888072921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5478633196793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.144080558646</t>
+    <t xml:space="preserve">56.5882112304725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8676081979791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.455819428452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Thomas Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.5733332647189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.538836813005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.112170077724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Didrik Tønseth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4916954551763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0041313055161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.495826760692</t>
   </si>
   <si>
     <t xml:space="preserve">Friedrich Moch</t>
@@ -152,55 +194,25 @@
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8880289776873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1672928397849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.055321817472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gus Schumacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5699391939964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.5493052534486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5167733962721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.636017843717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Didrik Tønseth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4849900494747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.5217735379137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.006763587388</t>
+    <t xml:space="preserve">58.6244729978396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7880147364668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.412487734306</t>
   </si>
   <si>
     <t xml:space="preserve">Erik Valnes</t>
   </si>
   <si>
-    <t xml:space="preserve">57.0722035568934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1258287046939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.198032261587</t>
+    <t xml:space="preserve">57.0722035570259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2741165897837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.34632014681</t>
   </si>
   <si>
     <t xml:space="preserve">William Poromaa</t>
@@ -209,40 +221,40 @@
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5779207004481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2524957810055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8304164814536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Thomas Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.673120884296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0270047947397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7001256790358</t>
+    <t xml:space="preserve">44.3421347265574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4578294300193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7999641565767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andreas Fjorden Ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2916623968149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9076346113968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1992970082117</t>
   </si>
   <si>
     <t xml:space="preserve">Ben Ogden</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1778584612851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2149794025681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6411690278226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0340068916759</t>
+    <t xml:space="preserve">11.7936369463807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.214979402859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7865047510189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7951211002585</t>
   </si>
   <si>
     <t xml:space="preserve">Andrew Musgrave</t>
@@ -251,28 +263,55 @@
     <t xml:space="preserve">Great Britain</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2906779230518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93273840033505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.401259287127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6246756105139</t>
+    <t xml:space="preserve">37.7893615678098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93273840007712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3093038406183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0314038085051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zanden McMullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.257401844645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21214210964859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.6753165622374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.144860516531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edvin Anger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3325975127793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7027683479506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.0353658607299</t>
   </si>
   <si>
     <t xml:space="preserve">Calle Halfvarsson</t>
   </si>
   <si>
-    <t xml:space="preserve">36.27089846031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8271632893313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.0980617496413</t>
+    <t xml:space="preserve">28.7362972395019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7961993091322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.5324965486341</t>
   </si>
   <si>
     <t xml:space="preserve">Antoine Cyr</t>
@@ -281,85 +320,619 @@
     <t xml:space="preserve">Canada</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7249103767858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0267993765876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2738800717866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0255898251599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edvin Anger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3325975125187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.28133178558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6139292980987</t>
+    <t xml:space="preserve">21.7614659908964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0267993766856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0633206828486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.8515860504306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iivo Niskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.83823037117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72457560192664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.091499144049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6543051171456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Chanavat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1859432694895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Even Northug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6737697865377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Solås Taugbøl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6579355186439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florian Notz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7286246404531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.887823452763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6164480932161</t>
   </si>
   <si>
     <t xml:space="preserve">Hugo Lapalus</t>
   </si>
   <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1097520898675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4990396967271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6087917865946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Chanavat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1859432694522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Even Northug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6737697863801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iivo Niskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4708575566042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72457560189993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1216312675901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3170644260942</t>
+    <t xml:space="preserve">46.0498163388325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035965387115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.353412877544</t>
   </si>
   <si>
     <t xml:space="preserve">Joni Mäki</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6321922012688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.396737699424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0289299006928</t>
+    <t xml:space="preserve">54.6321922015736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05934817785738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6915403794309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davide Graz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6161980337023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6328010889707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.127733383202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3767325058749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Lapierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4753630826379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.202659035783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6780221184209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauri Vuorinen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.5843811597336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.630493817931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2148749776646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Häggström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9877565983356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8818841330007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8696407313363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iver Tildheim Andersen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.6354841800948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truls Gisselman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1230243454663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8792034754935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0022278209598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Davies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4286345417251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3576341234629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7862686651879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renaud Jay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7501667876148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irineu Esteve Altimiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andorra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9797842492291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.02172178851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0015060377391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathis Desloges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8288244491905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50690515733393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3357296065245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naoto Baba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8333310448352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5858488769563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4191799217915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mattis Stenshagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3717903072619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0007733069076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3725636141696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elia Barp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6798662289549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1940638305135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77720244295943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.6511325024278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Clinton Schoonmaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5090258592009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Chappaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8974054211142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98013378786954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08715676943059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9646959784143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arsi Ruuskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2866398581528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60548547815242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8921253363053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anian Sossau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7374686775284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9252816803841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02816173118756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6909120891001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Hellweger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0793099503325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.7109759817195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4801118197016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8440419148808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3241537345824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Johannes Alev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6844030301761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.142876237051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.827279267227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleksander Holmboe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1915681364008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Lindholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2258078899104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90419677570984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1300046656202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesco De Fabiani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5851384621148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3700054435592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.955143905674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo Schely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5835217691176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2682728598598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.8517946289774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matz William Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.640265652946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Simenc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5589956148669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6952696917364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6121803482616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8664456548649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oskar Svensson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1756438646904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ansgar Evensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4852700241061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hollmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9366700981266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.400382626251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3370527243776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Grate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5256946320645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Moseby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6019119458889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janosch Brugger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97981297490485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2306414796231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9320326394954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1424870940233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4888516730704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4484432549323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11599930118016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0532942291829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Leveille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3580506938451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10656162148988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.464612315335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sivert Wiig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4621169498848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Jouve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2965951937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Stoelben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7769180075668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zak Ketterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60268237269823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37145095198988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93750852645053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9116418511386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niilo Moilanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.293908610721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98660530072151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2805139114426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondrej Cerny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8323201443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Bourdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32904364928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1518100305283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4808536798123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludek Seller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2705287229584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone Dapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8503505252228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.055349240326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0696290827756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9753288483244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Måns Skoglund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1985386607803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauri Lepistö</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5592062582008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.306819993719947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17129374106135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0373199929821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Myhlback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69925284361758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40238239223089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1016352358485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryo Hirose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49461438481228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10767222597184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6022866107841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Ekberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5305340567661</t>
   </si>
   <si>
     <t xml:space="preserve">Beda Klee</t>
@@ -368,586 +941,124 @@
     <t xml:space="preserve">Switzerland</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2457368911953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.770673595043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0164104862383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Håvard Solås Taugbøl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6579355183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Lapierre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.32834330695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41694898386876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7452922908187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Häggström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9877565979925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3552188626527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3429754606451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iver Tildheim Andersen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.9968898281222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Vuorinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.5843811593737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8265698029202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4109509622939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davide Graz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.751397624873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6328010889937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47040039435951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8545991082262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renaud Jay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7501667873065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.687619561980568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4377863492871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florian Notz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.392450255265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0910781772996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4835284325646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesco De Fabiani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5851384623103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6256146264824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2107530887927</t>
+    <t xml:space="preserve">1.44175603787663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14878035595961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59053639383624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Wonders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76150682501907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13998696474679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90149378976587</t>
   </si>
   <si>
     <t xml:space="preserve">Cyril Fähndrich</t>
   </si>
   <si>
-    <t xml:space="preserve">23.161579658636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73175931978158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3569123921103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2502513705279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mattis Stenshagen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8858506034725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0007733069361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8866239104085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naoto Baba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7436012589393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1754415551173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9190428140566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elia Barp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5672157999664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1940638305249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97514966518391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7364292956752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zanden McMullen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.78442723455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21214210977304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4655650264823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4621343708054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Clinton Schoonmaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5090258588723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Hellweger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.079309950216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26532265910586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.3446326093219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Irineu Esteve Altimiras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andorra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3335483142343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3888779313734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7224262456076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Chappaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3661182789358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98013378774928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73522693241881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.0814789991039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.7109759816374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Jouve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2965951934966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2905515266259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.5871467201225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theo Schely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58352176910395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.682010176558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.2655319456619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aleksander Holmboe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1915681367435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matz William Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6402656528161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oskar Svensson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1756438644405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ansgar Evensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4852700238532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anian Sossau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21021618139246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9252816803752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30990734037162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4454052021393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ireland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3031166205495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.637067223236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9401838437855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Grate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5256946318571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Håvard Moseby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.967885157318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2454293447694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4484432549945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75296028171128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4468328814751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Stoelben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45169839257621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7769180075485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.03886323772942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2674796378542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Lindholm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9407458988861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43472328133296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3754691802191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simone Dapra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2334228334191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05534924039439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14562679927692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4343988730904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truls Gisselman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90252760857777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1435198467276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0460474553054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sivert Wiig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4621169499297</t>
+    <t xml:space="preserve">6.73175931963002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99003483559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72179415522145</t>
   </si>
   <si>
     <t xml:space="preserve">Paolo Ventura</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6340375440875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92738177075717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5614193148446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsi Ruuskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6378162015318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67644651854232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3142627200741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niilo Moilanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.293908610581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0837394814931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3776480920741</t>
+    <t xml:space="preserve">7.15947468395292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.699531586561657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85900627051458</t>
   </si>
   <si>
     <t xml:space="preserve">Albert Kuchler</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64800458800578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32823013454632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9762347225521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondrej Cerny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8323201442294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Bourdin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32904364931418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2471902274679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5762338767821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Davies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15025151918066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19467509545427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3449266146349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludek Seller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2705287228842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zak Ketterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63410598570202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37145095200594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77836902011038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7839259578183</t>
+    <t xml:space="preserve">7.6480485111647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marko Kilp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76576208812114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnus Øyaas Håbrekke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37029790654521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier McKeever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.365030464336623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77826920034807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00369614099583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14699580568052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Liekari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04584118621569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matyas Bauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44131872235263</t>
   </si>
   <si>
     <t xml:space="preserve">Johnny Hagenbuch</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69645538965557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23547409185064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22518314128085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1571126227871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Myhlback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94321113906101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76206543667578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7052765757368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter Wonders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77102101297235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25006198909287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0210830020652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryo Hirose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9326465994003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50162442051242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4342710199127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janosch Brugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49276712307096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23064147974305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66902118709038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3924297899044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Lepistö</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98142760110982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.306819993758382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0598510001165155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34809859498472</t>
+    <t xml:space="preserve">4.23547409173043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simeon Deyanov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80848371357504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Himma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5069670909491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominik Bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47162180418234</t>
   </si>
   <si>
     <t xml:space="preserve">Vitaliy Pukhkalo</t>
@@ -956,316 +1067,154 @@
     <t xml:space="preserve">Kazakhstan</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53384427422523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24442421355694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77826848778217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hollmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80307763616539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91456370591174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71764134207713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Liekari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04584118625368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56871430424584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61455549049952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olivier Leveille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85569582890601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32008273279963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17577856170564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathis Desloges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32220124678902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64656253147136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96876377826038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Johannes Alev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20198326607999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.587189822601452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78917308868144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marko Kilp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76576208816174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Simenc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69526969181425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnus Øyaas Håbrekke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37029790676678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andreas Fjorden Ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65449554813551</t>
+    <t xml:space="preserve">2.70612367874116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haruki Yamashita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49510073409039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.479878968825905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97497970291629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri Tuz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71196299821339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57163045513154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eero Rantala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.536796032795671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gabriel Gledhill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15803586780951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daito YAMAZAKI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sander HAUKVIK-JENSEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einar HEDEGART</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ole Tafjord SUHRKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fredrik FODSTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian ENDRESTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einar Hedegart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ole Tafjord Suhrke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sander Haukvik Jensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Earnhart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136243853438111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oskar Opstad Vike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lars Young Vik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seve De Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ji-Yeong Byun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oleksandr Lisohor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niks Saulitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jong-Won Jeong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentley Walker-Broose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Büki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Konya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anton Grahn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomas Dufek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imanol Rojo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Fellner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauris Kaparkalejs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathias Holbæk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fedor Karpov</t>
   </si>
   <si>
     <t xml:space="preserve">Sasha Masson</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50910229061506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48496947766066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99407176827573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haruki Yamashita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06040288197169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05959853896316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12000142093485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Himma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50696709107414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imanol Rojo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47234469140973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominik Bury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47111554658649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Fellner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13577552004622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149118503147054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28489402319327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier McKeever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47634341325807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77826920042445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25461261368252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eero Rantala</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05484512961513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.324478275824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matyas Bauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19080925669991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiri Tuz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71196299840381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gabriel Gledhill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.06062036109426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Earnhart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136243853481135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oskar Opstad Vike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Måns Skoglund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nail Bashmakov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lars Young Vik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simeon Deyanov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seve De Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Ekberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ji-Yeong Byun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Korea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oleksandr Lisohor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niks Saulitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jong-Won Jeong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bentley Walker-Broose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Büki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Konya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daito YAMAZAKI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sander HAUKVIK-JENSEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einar HEDEGART</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ole Tafjord SUHRKE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fredrik FODSTAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian ENDRESTAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anton Grahn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomas Dufek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauris Kaparkalejs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathias Holbæk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fedor Karpov</t>
-  </si>
-  <si>
     <t xml:space="preserve">Olzhas Klimin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einar Hedegart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ole Tafjord Suhrke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sander Haukvik Jensen</t>
   </si>
   <si>
     <t xml:space="preserve">Nicolai Elde Holmboe</t>
@@ -1721,126 +1670,126 @@
         <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -1849,24 +1798,24 @@
         <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>0.554369703815855</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
@@ -1875,68 +1824,68 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
         <v>52</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
         <v>53</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>56</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
         <v>57</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" t="s">
         <v>59</v>
       </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="G12" t="s">
         <v>61</v>
@@ -1953,36 +1902,36 @@
         <v>63</v>
       </c>
       <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
         <v>64</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
         <v>65</v>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
         <v>66</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" t="s">
         <v>68</v>
-      </c>
-      <c r="B14" t="s">
-        <v>10</v>
       </c>
       <c r="C14" t="s">
         <v>69</v>
@@ -2011,7 +1960,7 @@
         <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
         <v>73</v>
@@ -2020,68 +1969,68 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>74</v>
       </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
         <v>75</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.895538608879911</v>
-      </c>
-      <c r="I15" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
         <v>77</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
         <v>78</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
         <v>79</v>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="H16" t="n">
+        <v>0.895538608879911</v>
+      </c>
+      <c r="I16" t="s">
         <v>80</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" t="s">
         <v>83</v>
       </c>
-      <c r="B17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
         <v>84</v>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>16</v>
-      </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="s">
         <v>85</v>
@@ -2098,100 +2047,100 @@
         <v>87</v>
       </c>
       <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
         <v>88</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
         <v>89</v>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="n">
+        <v>0.895538608879911</v>
+      </c>
+      <c r="G18" t="s">
         <v>90</v>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
         <v>91</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
         <v>93</v>
       </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
         <v>94</v>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
         <v>95</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
         <v>97</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="s">
         <v>98</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
         <v>99</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.140598576859704</v>
-      </c>
-      <c r="G20" t="s">
-        <v>100</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.343380738512093</v>
-      </c>
-      <c r="I20" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
         <v>102</v>
       </c>
-      <c r="B21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
         <v>103</v>
@@ -2200,79 +2149,79 @@
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="H21" t="n">
-        <v>0.232048869591992</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>16</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F23" t="n">
-        <v>0.343380738512093</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>0.343380738512093</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="I23" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -2281,74 +2230,74 @@
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
         <v>118</v>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>16</v>
-      </c>
       <c r="F25" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.203941216842155</v>
+      </c>
+      <c r="G26" t="s">
         <v>121</v>
       </c>
-      <c r="B26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="s">
-        <v>16</v>
-      </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="s">
         <v>122</v>
@@ -2359,7 +2308,7 @@
         <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
         <v>124</v>
@@ -2371,13 +2320,13 @@
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>0.23180786429876</v>
+        <v>0.140598576859704</v>
       </c>
       <c r="G27" t="s">
         <v>125</v>
       </c>
       <c r="H27" t="n">
-        <v>0.126322714192866</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="I27" t="s">
         <v>126</v>
@@ -2388,7 +2337,7 @@
         <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
         <v>16</v>
@@ -2417,7 +2366,7 @@
         <v>131</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
         <v>132</v>
@@ -2426,85 +2375,85 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.47308066914478</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.779978161976048</v>
       </c>
       <c r="I29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.23180786429876</v>
       </c>
       <c r="G30" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0.126322714192866</v>
       </c>
       <c r="I30" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F31" t="n">
-        <v>0.47308066914478</v>
+        <v>1</v>
       </c>
       <c r="G31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H31" t="n">
-        <v>0.779978161976048</v>
+        <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
         <v>16</v>
@@ -2513,30 +2462,30 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H32" t="n">
-        <v>0.382583907138237</v>
+        <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
@@ -2545,13 +2494,13 @@
         <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.203941216842155</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="s">
         <v>149</v>
@@ -2562,19 +2511,19 @@
         <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
         <v>152</v>
@@ -2591,7 +2540,7 @@
         <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
         <v>155</v>
@@ -2600,37 +2549,37 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="s">
         <v>156</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
         <v>157</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.755081337596291</v>
-      </c>
-      <c r="I35" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>158</v>
+      </c>
+      <c r="B36" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
         <v>159</v>
       </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>160</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>161</v>
-      </c>
       <c r="F36" t="n">
         <v>1</v>
       </c>
@@ -2638,114 +2587,114 @@
         <v>16</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="I36" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
         <v>163</v>
       </c>
-      <c r="B37" t="s">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
         <v>164</v>
-      </c>
-      <c r="C37" t="s">
-        <v>165</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.558971169677543</v>
-      </c>
-      <c r="G37" t="s">
-        <v>166</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" t="s">
+        <v>166</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>167</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.208270945862351</v>
+      </c>
+      <c r="I38" t="s">
         <v>168</v>
-      </c>
-      <c r="B38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>170</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.779978161976048</v>
-      </c>
-      <c r="G38" t="s">
-        <v>171</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.47308066914478</v>
-      </c>
-      <c r="I38" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" t="s">
+        <v>170</v>
+      </c>
+      <c r="C39" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.558971169677543</v>
+      </c>
+      <c r="G39" t="s">
+        <v>172</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
         <v>173</v>
-      </c>
-      <c r="B39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C39" t="s">
-        <v>174</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>175</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.895538608879911</v>
-      </c>
-      <c r="G39" t="s">
-        <v>176</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>175</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -2754,192 +2703,192 @@
         <v>16</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
         <v>180</v>
       </c>
-      <c r="B41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="n">
+        <v>0.779978161976048</v>
+      </c>
+      <c r="G41" t="s">
         <v>181</v>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
+      <c r="H41" t="n">
+        <v>0.47308066914478</v>
+      </c>
+      <c r="I41" t="s">
         <v>182</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>183</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="s">
         <v>184</v>
       </c>
-      <c r="B42" t="s">
-        <v>185</v>
-      </c>
-      <c r="C42" t="s">
-        <v>186</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>16</v>
-      </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>187</v>
+        <v>16</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B43" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D43" t="n">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F43" t="n">
         <v>0.382186556584935</v>
       </c>
       <c r="G43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H43" t="n">
         <v>0.0766185991760893</v>
       </c>
       <c r="I43" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>191</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>195</v>
+        <v>16</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0.0766185991760893</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.208270945862351</v>
       </c>
       <c r="I44" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" t="s">
+        <v>195</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="s">
         <v>196</v>
       </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" t="s">
-        <v>16</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
         <v>197</v>
       </c>
-      <c r="F45" t="n">
-        <v>0.630774225526373</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="H45" t="n">
+        <v>0.336242222180128</v>
+      </c>
+      <c r="I45" t="s">
         <v>198</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.630774225526373</v>
-      </c>
-      <c r="I45" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
         <v>200</v>
       </c>
-      <c r="B46" t="s">
-        <v>98</v>
-      </c>
-      <c r="C46" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="s">
-        <v>201</v>
-      </c>
       <c r="F46" t="n">
-        <v>0.382583907138237</v>
+        <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>16</v>
@@ -2948,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -2960,33 +2909,33 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" t="s">
+        <v>205</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
         <v>206</v>
       </c>
-      <c r="B48" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="s">
-        <v>207</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="s">
-        <v>16</v>
-      </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="s">
         <v>207</v>
@@ -2997,33 +2946,33 @@
         <v>208</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>209</v>
+        <v>16</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s">
         <v>10</v>
@@ -3035,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F50" t="n">
         <v>1</v>
@@ -3047,73 +2996,73 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>214</v>
+        <v>16</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0.126322714192866</v>
       </c>
       <c r="G51" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H51" t="n">
-        <v>0.336242222180128</v>
+        <v>0.126322714192866</v>
       </c>
       <c r="I51" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B52" t="s">
-        <v>218</v>
+        <v>31</v>
       </c>
       <c r="C52" t="s">
-        <v>219</v>
+        <v>16</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="s">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="F52" t="n">
         <v>1</v>
       </c>
       <c r="G52" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="C53" t="s">
         <v>16</v>
@@ -3122,24 +3071,24 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>225</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -3151,169 +3100,169 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>16</v>
+        <v>228</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>225</v>
+        <v>16</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="C55" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="H55" t="n">
-        <v>0.669620389113773</v>
+        <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C56" t="s">
-        <v>232</v>
+        <v>16</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="s">
-        <v>234</v>
+        <v>16</v>
       </c>
       <c r="H56" t="n">
-        <v>0.203941216842155</v>
+        <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>237</v>
+        <v>16</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>16</v>
+        <v>238</v>
       </c>
       <c r="F57" t="n">
-        <v>0.126322714192866</v>
+        <v>1</v>
       </c>
       <c r="G57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="s">
         <v>238</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.126322714192866</v>
-      </c>
-      <c r="I57" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>239</v>
+      </c>
+      <c r="B58" t="s">
+        <v>101</v>
+      </c>
+      <c r="C58" t="s">
         <v>240</v>
       </c>
-      <c r="B58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.788467781907967</v>
+      </c>
+      <c r="G58" t="s">
         <v>241</v>
       </c>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
         <v>242</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.286937930353677</v>
-      </c>
-      <c r="G58" t="s">
-        <v>243</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.174036652193994</v>
-      </c>
-      <c r="I58" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C59" t="s">
-        <v>246</v>
+        <v>16</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>247</v>
+        <v>16</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B60" t="s">
         <v>10</v>
@@ -3325,143 +3274,143 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>250</v>
+        <v>16</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>247</v>
+      </c>
+      <c r="B61" t="s">
+        <v>59</v>
+      </c>
+      <c r="C61" t="s">
+        <v>248</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="s">
+        <v>249</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="G61" t="s">
+        <v>250</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="I61" t="s">
         <v>251</v>
-      </c>
-      <c r="B61" t="s">
-        <v>29</v>
-      </c>
-      <c r="C61" t="s">
-        <v>252</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>16</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.174036652193994</v>
-      </c>
-      <c r="G61" t="s">
-        <v>253</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.286937930353677</v>
-      </c>
-      <c r="I61" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>252</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>253</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>254</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
         <v>255</v>
       </c>
-      <c r="B62" t="s">
-        <v>107</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="H62" t="n">
+        <v>0.669620389113773</v>
+      </c>
+      <c r="I62" t="s">
         <v>256</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.0766185991760893</v>
-      </c>
-      <c r="G62" t="s">
-        <v>257</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.208270945862351</v>
-      </c>
-      <c r="I62" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>257</v>
+      </c>
+      <c r="B63" t="s">
+        <v>101</v>
+      </c>
+      <c r="C63" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.290061086989989</v>
+      </c>
+      <c r="G63" t="s">
         <v>259</v>
       </c>
-      <c r="B63" t="s">
-        <v>107</v>
-      </c>
-      <c r="C63" t="s">
-        <v>16</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="H63" t="n">
+        <v>0.478229883922796</v>
+      </c>
+      <c r="I63" t="s">
         <v>260</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.630774225526373</v>
-      </c>
-      <c r="G63" t="s">
-        <v>261</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.382583907138237</v>
-      </c>
-      <c r="I63" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>264</v>
+        <v>16</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>16</v>
+        <v>262</v>
       </c>
       <c r="F64" t="n">
-        <v>0.336242222180128</v>
+        <v>1</v>
       </c>
       <c r="G64" t="s">
-        <v>265</v>
+        <v>16</v>
       </c>
       <c r="H64" t="n">
-        <v>0.554369703815855</v>
+        <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B65" t="s">
-        <v>268</v>
+        <v>113</v>
       </c>
       <c r="C65" t="s">
         <v>16</v>
@@ -3470,85 +3419,85 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="G65" t="s">
         <v>16</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="I65" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B66" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C66" t="s">
         <v>16</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F66" t="n">
-        <v>0.232048869591992</v>
+        <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>272</v>
+        <v>16</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>0.203941216842155</v>
       </c>
       <c r="I66" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B67" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>16</v>
+        <v>269</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>0.329450242982193</v>
       </c>
       <c r="G67" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0.543171623242067</v>
       </c>
       <c r="I67" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B68" t="s">
-        <v>268</v>
+        <v>107</v>
       </c>
       <c r="C68" t="s">
         <v>16</v>
@@ -3557,146 +3506,146 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="G68" t="s">
-        <v>16</v>
+        <v>274</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="I68" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>277</v>
       </c>
       <c r="C69" t="s">
-        <v>281</v>
+        <v>16</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F69" t="n">
-        <v>0.329450242982193</v>
+        <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c r="H69" t="n">
-        <v>0.543171623242067</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B70" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="C70" t="s">
-        <v>286</v>
+        <v>16</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F70" t="n">
-        <v>0.543171623242067</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="G70" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="H70" t="n">
-        <v>0.121197971282085</v>
+        <v>1</v>
       </c>
       <c r="I70" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>277</v>
       </c>
       <c r="C71" t="s">
-        <v>291</v>
+        <v>16</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="s">
-        <v>292</v>
+        <v>16</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
       </c>
       <c r="I71" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>16</v>
+        <v>287</v>
       </c>
       <c r="F72" t="n">
-        <v>0.121197971282085</v>
+        <v>0.286937930353677</v>
       </c>
       <c r="G72" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H72" t="n">
-        <v>0.329450242982193</v>
+        <v>0.174036652193994</v>
       </c>
       <c r="I72" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B73" t="s">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
@@ -3705,85 +3654,85 @@
         <v>16</v>
       </c>
       <c r="F73" t="n">
-        <v>0.921587657155495</v>
+        <v>0</v>
       </c>
       <c r="G73" t="s">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="H73" t="n">
-        <v>0.921587657155495</v>
+        <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F74" t="n">
-        <v>0.914001122512931</v>
+        <v>0.208270945862351</v>
       </c>
       <c r="G74" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="H74" t="n">
-        <v>0.914001122512931</v>
+        <v>0.0766185991760893</v>
       </c>
       <c r="I74" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C75" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>309</v>
+        <v>16</v>
       </c>
       <c r="F75" t="n">
-        <v>0.208270945862351</v>
+        <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0766185991760893</v>
+        <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B76" t="s">
-        <v>313</v>
+        <v>170</v>
       </c>
       <c r="C76" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -3792,27 +3741,27 @@
         <v>16</v>
       </c>
       <c r="F76" t="n">
-        <v>0.406145296366207</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="G76" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="I76" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B77" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="C77" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -3821,56 +3770,56 @@
         <v>16</v>
       </c>
       <c r="F77" t="n">
-        <v>0.788467781907967</v>
+        <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>319</v>
+        <v>16</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>308</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>309</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>322</v>
+        <v>16</v>
       </c>
       <c r="F78" t="n">
-        <v>0.382583907138237</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G78" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="H78" t="n">
-        <v>0.232048869591992</v>
+        <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -3879,56 +3828,56 @@
         <v>16</v>
       </c>
       <c r="F79" t="n">
-        <v>0.290061086989989</v>
+        <v>0.121197971282085</v>
       </c>
       <c r="G79" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="H79" t="n">
-        <v>0.478229883922796</v>
+        <v>0.329450242982193</v>
       </c>
       <c r="I79" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="C80" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>16</v>
+        <v>317</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="H80" t="n">
-        <v>0.208270945862351</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I80" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="B81" t="s">
-        <v>334</v>
+        <v>31</v>
       </c>
       <c r="C81" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -3937,24 +3886,24 @@
         <v>16</v>
       </c>
       <c r="F81" t="n">
-        <v>0.558971169677543</v>
+        <v>0.174036652193994</v>
       </c>
       <c r="G81" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0.286937930353677</v>
       </c>
       <c r="I81" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="B82" t="s">
-        <v>334</v>
+        <v>59</v>
       </c>
       <c r="C82" t="s">
         <v>16</v>
@@ -3963,27 +3912,27 @@
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>339</v>
+        <v>16</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0.336242222180128</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>325</v>
       </c>
       <c r="H82" t="n">
-        <v>0.558971169677543</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="I82" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s">
-        <v>341</v>
+        <v>209</v>
       </c>
       <c r="C83" t="s">
         <v>16</v>
@@ -3992,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="F83" t="n">
         <v>1</v>
@@ -4001,15 +3950,15 @@
         <v>16</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="I83" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
@@ -4021,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="F84" t="n">
         <v>1</v>
@@ -4033,76 +3982,76 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="B85" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>331</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>332</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>0.478229883922796</v>
       </c>
       <c r="G85" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0.788467781907967</v>
       </c>
       <c r="I85" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="C86" t="s">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>16</v>
+        <v>336</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="G86" t="s">
-        <v>349</v>
+        <v>16</v>
       </c>
       <c r="H86" t="n">
-        <v>0.290061086989989</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="I86" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="B87" t="s">
-        <v>164</v>
+        <v>277</v>
       </c>
       <c r="C87" t="s">
-        <v>352</v>
+        <v>16</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
@@ -4111,24 +4060,24 @@
         <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="H87" t="n">
-        <v>0.558971169677543</v>
+        <v>0.910108467846823</v>
       </c>
       <c r="I87" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B88" t="s">
-        <v>334</v>
+        <v>25</v>
       </c>
       <c r="C88" t="s">
         <v>16</v>
@@ -4137,30 +4086,30 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="F88" t="n">
-        <v>0.921587657155495</v>
+        <v>0.543171623242067</v>
       </c>
       <c r="G88" t="s">
         <v>16</v>
       </c>
       <c r="H88" t="n">
-        <v>0.921587657155495</v>
+        <v>0.121197971282085</v>
       </c>
       <c r="I88" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="B89" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="C89" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
@@ -4178,47 +4127,47 @@
         <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="B90" t="s">
-        <v>361</v>
+        <v>209</v>
       </c>
       <c r="C90" t="s">
-        <v>362</v>
+        <v>16</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>16</v>
+        <v>345</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="G90" t="s">
         <v>16</v>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="I90" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="B91" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="C91" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
@@ -4227,114 +4176,114 @@
         <v>16</v>
       </c>
       <c r="F91" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G91" t="s">
-        <v>365</v>
+        <v>16</v>
       </c>
       <c r="H91" t="n">
-        <v>0.552008689413187</v>
+        <v>1</v>
       </c>
       <c r="I91" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="B92" t="s">
-        <v>88</v>
+        <v>350</v>
       </c>
       <c r="C92" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>369</v>
+        <v>16</v>
       </c>
       <c r="F92" t="n">
-        <v>0.478229883922796</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G92" t="s">
         <v>16</v>
       </c>
       <c r="H92" t="n">
-        <v>0.788467781907967</v>
+        <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="B93" t="s">
-        <v>107</v>
+        <v>170</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>353</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="s">
         <v>16</v>
       </c>
       <c r="F93" t="n">
-        <v>0.232048869591992</v>
+        <v>1</v>
       </c>
       <c r="G93" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="H93" t="n">
-        <v>0.630774225526373</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="I93" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B94" t="s">
-        <v>341</v>
+        <v>277</v>
       </c>
       <c r="C94" t="s">
-        <v>374</v>
+        <v>16</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="F94" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G94" t="s">
         <v>16</v>
       </c>
       <c r="H94" t="n">
-        <v>0.755081337596291</v>
+        <v>0.334810194556887</v>
       </c>
       <c r="I94" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B95" t="s">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>359</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -4343,56 +4292,56 @@
         <v>16</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G95" t="s">
-        <v>376</v>
+        <v>16</v>
       </c>
       <c r="H95" t="n">
-        <v>0.910108467846823</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I95" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="B96" t="s">
-        <v>268</v>
+        <v>107</v>
       </c>
       <c r="C96" t="s">
         <v>16</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>378</v>
+        <v>16</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
+        <v>361</v>
       </c>
       <c r="H96" t="n">
-        <v>0.334810194556887</v>
+        <v>0.630774225526373</v>
       </c>
       <c r="I96" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B97" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -4404,62 +4353,58 @@
         <v>0.74529489290339</v>
       </c>
       <c r="G97" t="s">
-        <v>380</v>
+        <v>16</v>
       </c>
       <c r="H97" t="n">
         <v>0.406145296366207</v>
       </c>
       <c r="I97" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>381</v>
-      </c>
-      <c r="B98" t="s">
-        <v>50</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="B98"/>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>382</v>
+        <v>16</v>
       </c>
       <c r="F98" t="n">
-        <v>0.199821673218477</v>
+        <v>0</v>
       </c>
       <c r="G98" t="s">
         <v>16</v>
       </c>
       <c r="H98" t="n">
-        <v>0.199821673218477</v>
+        <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>383</v>
-      </c>
-      <c r="B99" t="s">
-        <v>10</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="B99"/>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" t="s">
         <v>16</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="s">
         <v>16</v>
@@ -4468,18 +4413,16 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>384</v>
-      </c>
-      <c r="B100" t="s">
-        <v>64</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="B100"/>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D100" t="n">
         <v>1</v>
@@ -4497,18 +4440,16 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>385</v>
-      </c>
-      <c r="B101" t="s">
-        <v>313</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="B101"/>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
@@ -4517,27 +4458,25 @@
         <v>16</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="s">
         <v>16</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>386</v>
-      </c>
-      <c r="B102" t="s">
-        <v>387</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="B102"/>
       <c r="C102" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -4546,27 +4485,25 @@
         <v>16</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" t="s">
         <v>16</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>388</v>
-      </c>
-      <c r="B103" t="s">
-        <v>389</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="B103"/>
       <c r="C103" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
@@ -4575,27 +4512,27 @@
         <v>16</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="s">
         <v>16</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="B104" t="s">
-        <v>387</v>
+        <v>10</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
@@ -4604,27 +4541,27 @@
         <v>16</v>
       </c>
       <c r="F104" t="n">
-        <v>0.558971169677543</v>
+        <v>0</v>
       </c>
       <c r="G104" t="s">
         <v>16</v>
       </c>
       <c r="H104" t="n">
-        <v>0.921587657155495</v>
+        <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="B105" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
@@ -4642,18 +4579,18 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="B106" t="s">
-        <v>393</v>
+        <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
@@ -4668,18 +4605,18 @@
         <v>16</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>16</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="B107" t="s">
-        <v>395</v>
+        <v>25</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -4688,45 +4625,45 @@
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>16</v>
+        <v>374</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0.199821673218477</v>
       </c>
       <c r="G107" t="s">
         <v>16</v>
       </c>
       <c r="H107" t="n">
-        <v>1</v>
+        <v>0.199821673218477</v>
       </c>
       <c r="I107" t="s">
-        <v>16</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="B108" t="s">
-        <v>397</v>
+        <v>10</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
       </c>
       <c r="F108" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G108" t="s">
         <v>16</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" t="s">
         <v>16</v>
@@ -4734,10 +4671,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
       <c r="B109" t="s">
-        <v>393</v>
+        <v>350</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -4755,7 +4692,7 @@
         <v>16</v>
       </c>
       <c r="H109" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I109" t="s">
         <v>16</v>
@@ -4763,10 +4700,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="B110" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C110" t="s">
         <v>16</v>
@@ -4778,13 +4715,13 @@
         <v>16</v>
       </c>
       <c r="F110" t="n">
-        <v>0.921587657155495</v>
+        <v>1</v>
       </c>
       <c r="G110" t="s">
         <v>16</v>
       </c>
       <c r="H110" t="n">
-        <v>0.558971169677543</v>
+        <v>1</v>
       </c>
       <c r="I110" t="s">
         <v>16</v>
@@ -4792,10 +4729,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="B111" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="C111" t="s">
         <v>16</v>
@@ -4807,13 +4744,13 @@
         <v>16</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="G111" t="s">
         <v>16</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="I111" t="s">
         <v>16</v>
@@ -4821,10 +4758,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="B112" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="C112" t="s">
         <v>16</v>
@@ -4836,13 +4773,13 @@
         <v>16</v>
       </c>
       <c r="F112" t="n">
-        <v>0.755081337596291</v>
+        <v>0</v>
       </c>
       <c r="G112" t="s">
         <v>16</v>
       </c>
       <c r="H112" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I112" t="s">
         <v>16</v>
@@ -4850,9 +4787,11 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>403</v>
-      </c>
-      <c r="B113"/>
+        <v>382</v>
+      </c>
+      <c r="B113" t="s">
+        <v>383</v>
+      </c>
       <c r="C113" t="s">
         <v>16</v>
       </c>
@@ -4863,13 +4802,13 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="s">
         <v>16</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="s">
         <v>16</v>
@@ -4877,9 +4816,11 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>404</v>
-      </c>
-      <c r="B114"/>
+        <v>384</v>
+      </c>
+      <c r="B114" t="s">
+        <v>385</v>
+      </c>
       <c r="C114" t="s">
         <v>16</v>
       </c>
@@ -4890,13 +4831,13 @@
         <v>16</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G114" t="s">
         <v>16</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="s">
         <v>16</v>
@@ -4904,9 +4845,11 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>405</v>
-      </c>
-      <c r="B115"/>
+        <v>386</v>
+      </c>
+      <c r="B115" t="s">
+        <v>381</v>
+      </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
@@ -4917,13 +4860,13 @@
         <v>16</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" t="s">
         <v>16</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I115" t="s">
         <v>16</v>
@@ -4931,9 +4874,11 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>406</v>
-      </c>
-      <c r="B116"/>
+        <v>387</v>
+      </c>
+      <c r="B116" t="s">
+        <v>378</v>
+      </c>
       <c r="C116" t="s">
         <v>16</v>
       </c>
@@ -4944,13 +4889,13 @@
         <v>16</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>0.921587657155495</v>
       </c>
       <c r="G116" t="s">
         <v>16</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>0.558971169677543</v>
       </c>
       <c r="I116" t="s">
         <v>16</v>
@@ -4958,9 +4903,11 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>407</v>
-      </c>
-      <c r="B117"/>
+        <v>388</v>
+      </c>
+      <c r="B117" t="s">
+        <v>389</v>
+      </c>
       <c r="C117" t="s">
         <v>16</v>
       </c>
@@ -4971,13 +4918,13 @@
         <v>16</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="s">
         <v>16</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117" t="s">
         <v>16</v>
@@ -4985,9 +4932,11 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>408</v>
-      </c>
-      <c r="B118"/>
+        <v>390</v>
+      </c>
+      <c r="B118" t="s">
+        <v>389</v>
+      </c>
       <c r="C118" t="s">
         <v>16</v>
       </c>
@@ -4998,13 +4947,13 @@
         <v>16</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G118" t="s">
         <v>16</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I118" t="s">
         <v>16</v>
@@ -5012,10 +4961,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="B119" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C119" t="s">
         <v>16</v>
@@ -5041,10 +4990,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="B120" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C120" t="s">
         <v>16</v>
@@ -5070,10 +5019,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="B121" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C121" t="s">
         <v>16</v>
@@ -5091,7 +5040,7 @@
         <v>16</v>
       </c>
       <c r="H121" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I121" t="s">
         <v>16</v>
@@ -5099,28 +5048,28 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>277</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" t="s">
         <v>16</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G122" t="s">
         <v>16</v>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>0.552008689413187</v>
       </c>
       <c r="I122" t="s">
         <v>16</v>
@@ -5128,10 +5077,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B123" t="s">
-        <v>313</v>
+        <v>385</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
@@ -5149,7 +5098,7 @@
         <v>16</v>
       </c>
       <c r="H123" t="n">
-        <v>0.406145296366207</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I123" t="s">
         <v>16</v>
@@ -5157,28 +5106,28 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B124" t="s">
-        <v>313</v>
+        <v>10</v>
       </c>
       <c r="C124" t="s">
         <v>16</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
       </c>
       <c r="F124" t="n">
-        <v>0.669620389113773</v>
+        <v>0</v>
       </c>
       <c r="G124" t="s">
         <v>16</v>
       </c>
       <c r="H124" t="n">
-        <v>0.669620389113773</v>
+        <v>1</v>
       </c>
       <c r="I124" t="s">
         <v>16</v>
@@ -5186,10 +5135,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="C125" t="s">
         <v>16</v>
@@ -5201,13 +5150,13 @@
         <v>16</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" t="s">
         <v>16</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I125" t="s">
         <v>16</v>
@@ -5215,10 +5164,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="B126" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="C126" t="s">
         <v>16</v>
@@ -5230,13 +5179,13 @@
         <v>16</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="s">
         <v>16</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>0.290061086989989</v>
       </c>
       <c r="I126" t="s">
         <v>16</v>
@@ -5244,10 +5193,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B127" t="s">
-        <v>10</v>
+        <v>350</v>
       </c>
       <c r="C127" t="s">
         <v>16</v>
@@ -5259,13 +5208,13 @@
         <v>16</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G127" t="s">
         <v>16</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I127" t="s">
         <v>16</v>
@@ -5273,7 +5222,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B128" t="s">
         <v>10</v>
@@ -5302,7 +5251,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="B129" t="s">
         <v>10</v>

--- a/public/post/drafts/weekly-picks/2025Lillehammer/men-points.xlsx
+++ b/public/post/drafts/weekly-picks/2025Lillehammer/men-points.xlsx
@@ -569,31 +569,31 @@
     <t xml:space="preserve">41.5090258592009</t>
   </si>
   <si>
+    <t xml:space="preserve">Arsi Ruuskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2866398581528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60548547815242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8921253363053</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jules Chappaz</t>
   </si>
   <si>
     <t xml:space="preserve">28.8974054211142</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98013378786954</t>
+    <t xml:space="preserve">8.96678768910737</t>
   </si>
   <si>
     <t xml:space="preserve">2.08715676943059</t>
   </si>
   <si>
-    <t xml:space="preserve">40.9646959784143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arsi Ruuskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2866398581528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60548547815242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.8921253363053</t>
+    <t xml:space="preserve">39.9513498796522</t>
   </si>
   <si>
     <t xml:space="preserve">Anian Sossau</t>
@@ -749,6 +749,18 @@
     <t xml:space="preserve">27.5256946320645</t>
   </si>
   <si>
+    <t xml:space="preserve">Olivier Leveille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3580506938451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4192967654913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7773474593364</t>
+  </si>
+  <si>
     <t xml:space="preserve">Håvard Moseby</t>
   </si>
   <si>
@@ -785,18 +797,6 @@
     <t xml:space="preserve">26.0532942291829</t>
   </si>
   <si>
-    <t xml:space="preserve">Olivier Leveille</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3580506938451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10656162148988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.464612315335</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sivert Wiig</t>
   </si>
   <si>
@@ -1004,6 +1004,12 @@
     <t xml:space="preserve">6.37029790654521</t>
   </si>
   <si>
+    <t xml:space="preserve">Emil Liekari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04584118621569</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xavier McKeever</t>
   </si>
   <si>
@@ -1013,16 +1019,10 @@
     <t xml:space="preserve">1.77826920034807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00369614099583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14699580568052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Liekari</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04584118621569</t>
+    <t xml:space="preserve">2.42836446168712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57166412637182</t>
   </si>
   <si>
     <t xml:space="preserve">Matyas Bauer</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">1.97497970291629</t>
   </si>
   <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57163045513154</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jiri Tuz</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71196299821339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57163045513154</t>
+    <t xml:space="preserve">1.55807202131444</t>
   </si>
   <si>
     <t xml:space="preserve">Eero Rantala</t>
@@ -1109,30 +1109,30 @@
     <t xml:space="preserve">Daito YAMAZAKI</t>
   </si>
   <si>
+    <t xml:space="preserve">Fredrik FODSTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sebastian ENDRESTAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einar HEDEGART</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sander HAUKVIK-JENSEN</t>
   </si>
   <si>
-    <t xml:space="preserve">Einar HEDEGART</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ole Tafjord SUHRKE</t>
   </si>
   <si>
-    <t xml:space="preserve">Fredrik FODSTAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sebastian ENDRESTAD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Einar Hedegart</t>
   </si>
   <si>
+    <t xml:space="preserve">Sander Haukvik Jensen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ole Tafjord Suhrke</t>
   </si>
   <si>
-    <t xml:space="preserve">Sander Haukvik Jensen</t>
-  </si>
-  <si>
     <t xml:space="preserve">Michael Earnhart</t>
   </si>
   <si>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">South Korea</t>
   </si>
   <si>
+    <t xml:space="preserve">Niks Saulitis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jong-Won Jeong</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oleksandr Lisohor</t>
   </si>
   <si>
     <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niks Saulitis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jong-Won Jeong</t>
   </si>
   <si>
     <t xml:space="preserve">Bentley Walker-Broose</t>
@@ -2320,7 +2320,7 @@
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>0.140598576859704</v>
+        <v>0.0766185991760893</v>
       </c>
       <c r="G27" t="s">
         <v>125</v>
@@ -2407,7 +2407,7 @@
         <v>16</v>
       </c>
       <c r="F30" t="n">
-        <v>0.23180786429876</v>
+        <v>0.126322714192866</v>
       </c>
       <c r="G30" t="s">
         <v>138</v>
@@ -2552,7 +2552,7 @@
         <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G35" t="s">
         <v>156</v>
@@ -2639,7 +2639,7 @@
         <v>16</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.208270945862351</v>
       </c>
       <c r="G38" t="s">
         <v>167</v>
@@ -2772,7 +2772,7 @@
         <v>185</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
         <v>186</v>
@@ -2781,45 +2781,45 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0766185991760893</v>
+      </c>
+      <c r="G43" t="s">
         <v>187</v>
       </c>
-      <c r="F43" t="n">
-        <v>0.382186556584935</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="H43" t="n">
+        <v>0.208270945862351</v>
+      </c>
+      <c r="I43" t="s">
         <v>188</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.0766185991760893</v>
-      </c>
-      <c r="I43" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>189</v>
+      </c>
+      <c r="B44" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" t="s">
         <v>190</v>
       </c>
-      <c r="B44" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
         <v>191</v>
       </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>16</v>
-      </c>
       <c r="F44" t="n">
-        <v>0.0766185991760893</v>
+        <v>0.343380738512093</v>
       </c>
       <c r="G44" t="s">
         <v>192</v>
       </c>
       <c r="H44" t="n">
-        <v>0.208270945862351</v>
+        <v>0.0766185991760893</v>
       </c>
       <c r="I44" t="s">
         <v>193</v>
@@ -3265,112 +3265,112 @@
         <v>245</v>
       </c>
       <c r="B60" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>246</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>0.290061086989989</v>
       </c>
       <c r="G60" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0.788467781907967</v>
       </c>
       <c r="I60" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>16</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>249</v>
+        <v>16</v>
       </c>
       <c r="F61" t="n">
-        <v>0.914001122512931</v>
+        <v>0</v>
       </c>
       <c r="G61" t="s">
         <v>250</v>
       </c>
       <c r="H61" t="n">
-        <v>0.914001122512931</v>
+        <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>251</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" t="s">
         <v>252</v>
       </c>
-      <c r="B62" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
         <v>253</v>
       </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="F62" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="G62" t="s">
         <v>254</v>
       </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="H62" t="n">
+        <v>0.914001122512931</v>
+      </c>
+      <c r="I62" t="s">
         <v>255</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.669620389113773</v>
-      </c>
-      <c r="I62" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>256</v>
+      </c>
+      <c r="B63" t="s">
+        <v>82</v>
+      </c>
+      <c r="C63" t="s">
         <v>257</v>
       </c>
-      <c r="B63" t="s">
-        <v>101</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
         <v>258</v>
       </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>16</v>
-      </c>
       <c r="F63" t="n">
-        <v>0.290061086989989</v>
+        <v>1</v>
       </c>
       <c r="G63" t="s">
         <v>259</v>
       </c>
       <c r="H63" t="n">
-        <v>0.478229883922796</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I63" t="s">
         <v>260</v>
@@ -3990,54 +3990,54 @@
         <v>330</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C85" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="s">
         <v>331</v>
       </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="s">
-        <v>332</v>
-      </c>
       <c r="F85" t="n">
-        <v>0.478229883922796</v>
+        <v>0.382583907138237</v>
       </c>
       <c r="G85" t="s">
-        <v>333</v>
+        <v>16</v>
       </c>
       <c r="H85" t="n">
-        <v>0.788467781907967</v>
+        <v>0.232048869591992</v>
       </c>
       <c r="I85" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
+        <v>332</v>
+      </c>
+      <c r="B86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" t="s">
+        <v>333</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>334</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.478229883922796</v>
+      </c>
+      <c r="G86" t="s">
         <v>335</v>
       </c>
-      <c r="B86" t="s">
-        <v>107</v>
-      </c>
-      <c r="C86" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="s">
-        <v>336</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.382583907138237</v>
-      </c>
-      <c r="G86" t="s">
-        <v>16</v>
-      </c>
       <c r="H86" t="n">
-        <v>0.232048869591992</v>
+        <v>0.478229883922796</v>
       </c>
       <c r="I86" t="s">
         <v>336</v>
@@ -4060,7 +4060,7 @@
         <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>0.334810194556887</v>
       </c>
       <c r="G87" t="s">
         <v>338</v>
@@ -4251,25 +4251,25 @@
         <v>356</v>
       </c>
       <c r="B94" t="s">
-        <v>277</v>
+        <v>230</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>357</v>
+        <v>16</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G94" t="s">
         <v>16</v>
       </c>
       <c r="H94" t="n">
-        <v>0.334810194556887</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I94" t="s">
         <v>357</v>
@@ -4280,25 +4280,25 @@
         <v>358</v>
       </c>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>277</v>
       </c>
       <c r="C95" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
         <v>359</v>
       </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="s">
-        <v>16</v>
-      </c>
       <c r="F95" t="n">
-        <v>0.755081337596291</v>
+        <v>0.910108467846823</v>
       </c>
       <c r="G95" t="s">
         <v>16</v>
       </c>
       <c r="H95" t="n">
-        <v>0.755081337596291</v>
+        <v>0.334810194556887</v>
       </c>
       <c r="I95" t="s">
         <v>359</v>
@@ -4350,7 +4350,7 @@
         <v>16</v>
       </c>
       <c r="F97" t="n">
-        <v>0.74529489290339</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G97" t="s">
         <v>16</v>
@@ -4773,7 +4773,7 @@
         <v>16</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G112" t="s">
         <v>16</v>
@@ -4802,7 +4802,7 @@
         <v>16</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G113" t="s">
         <v>16</v>
@@ -4819,7 +4819,7 @@
         <v>384</v>
       </c>
       <c r="B114" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C114" t="s">
         <v>16</v>
@@ -4831,13 +4831,13 @@
         <v>16</v>
       </c>
       <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" t="n">
         <v>0.755081337596291</v>
-      </c>
-      <c r="G114" t="s">
-        <v>16</v>
-      </c>
-      <c r="H114" t="n">
-        <v>1</v>
       </c>
       <c r="I114" t="s">
         <v>16</v>
@@ -4845,11 +4845,11 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>385</v>
+      </c>
+      <c r="B115" t="s">
         <v>386</v>
       </c>
-      <c r="B115" t="s">
-        <v>381</v>
-      </c>
       <c r="C115" t="s">
         <v>16</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>16</v>
       </c>
       <c r="H115" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I115" t="s">
         <v>16</v>
@@ -5005,7 +5005,7 @@
         <v>16</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>0.203072648183104</v>
       </c>
       <c r="G120" t="s">
         <v>16</v>
@@ -5063,7 +5063,7 @@
         <v>16</v>
       </c>
       <c r="F122" t="n">
-        <v>0.755081337596291</v>
+        <v>0.552008689413187</v>
       </c>
       <c r="G122" t="s">
         <v>16</v>
@@ -5080,7 +5080,7 @@
         <v>396</v>
       </c>
       <c r="B123" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C123" t="s">
         <v>16</v>
